--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/148.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/148.xlsx
@@ -426,13 +426,13 @@
         <v>-8.415038660785932</v>
       </c>
       <c r="E2">
-        <v>-7.71840536540543</v>
+        <v>-9.152567380827273</v>
       </c>
       <c r="F2">
-        <v>-1.021122846106639</v>
+        <v>-1.34043528559857</v>
       </c>
       <c r="G2">
-        <v>-9.745042247252563</v>
+        <v>-8.529771969024422</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.567510433972055</v>
       </c>
       <c r="E3">
-        <v>-8.544715830959342</v>
+        <v>-9.636611701102066</v>
       </c>
       <c r="F3">
-        <v>-0.8740652661898509</v>
+        <v>-1.11010275904575</v>
       </c>
       <c r="G3">
-        <v>-9.780272940137342</v>
+        <v>-8.354922571523792</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.664701783300817</v>
       </c>
       <c r="E4">
-        <v>-10.07661121527705</v>
+        <v>-10.76545038597914</v>
       </c>
       <c r="F4">
-        <v>-0.8203216174636218</v>
+        <v>-1.179780054764828</v>
       </c>
       <c r="G4">
-        <v>-9.591647948801702</v>
+        <v>-8.34491689287835</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.6811995158656</v>
       </c>
       <c r="E5">
-        <v>-11.48045063481632</v>
+        <v>-10.8565926085025</v>
       </c>
       <c r="F5">
-        <v>-0.7775223588631797</v>
+        <v>-1.080220233357161</v>
       </c>
       <c r="G5">
-        <v>-9.385369102540954</v>
+        <v>-8.297452250839616</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.622562455259891</v>
       </c>
       <c r="E6">
-        <v>-11.33232635291631</v>
+        <v>-12.10731973934064</v>
       </c>
       <c r="F6">
-        <v>-0.08584137609741212</v>
+        <v>-0.8559513561928341</v>
       </c>
       <c r="G6">
-        <v>-9.429468494801744</v>
+        <v>-7.89458955835722</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.493339633162677</v>
       </c>
       <c r="E7">
-        <v>-12.90863202593041</v>
+        <v>-12.53666626646744</v>
       </c>
       <c r="F7">
-        <v>-0.5826688081722632</v>
+        <v>-0.9004322006209592</v>
       </c>
       <c r="G7">
-        <v>-8.566131808944856</v>
+        <v>-8.011126670043039</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.303536985085852</v>
       </c>
       <c r="E8">
-        <v>-12.69715881169279</v>
+        <v>-13.03251816653872</v>
       </c>
       <c r="F8">
-        <v>-0.8320728374397356</v>
+        <v>-0.671520324163941</v>
       </c>
       <c r="G8">
-        <v>-8.802897625168329</v>
+        <v>-7.881940500813276</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.058330119871567</v>
       </c>
       <c r="E9">
-        <v>-14.70400713669524</v>
+        <v>-13.57478635637628</v>
       </c>
       <c r="F9">
-        <v>-0.3619834483924469</v>
+        <v>-0.5041031302211469</v>
       </c>
       <c r="G9">
-        <v>-9.587205766879924</v>
+        <v>-7.633432860791271</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.771067329446311</v>
       </c>
       <c r="E10">
-        <v>-14.01126394734782</v>
+        <v>-14.11673890215316</v>
       </c>
       <c r="F10">
-        <v>0.2057439496880138</v>
+        <v>-0.5116205644015525</v>
       </c>
       <c r="G10">
-        <v>-8.630105494405496</v>
+        <v>-7.318001393920668</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.450866655443131</v>
       </c>
       <c r="E11">
-        <v>-14.03435164910254</v>
+        <v>-15.21699518669276</v>
       </c>
       <c r="F11">
-        <v>0.2471333269688911</v>
+        <v>-0.1321388302398765</v>
       </c>
       <c r="G11">
-        <v>-8.086539332929641</v>
+        <v>-6.969754172912068</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.118693070508386</v>
       </c>
       <c r="E12">
-        <v>-15.33703130040296</v>
+        <v>-16.19684572171426</v>
       </c>
       <c r="F12">
-        <v>0.6219530093876114</v>
+        <v>-0.1986252547233704</v>
       </c>
       <c r="G12">
-        <v>-8.066718559993911</v>
+        <v>-6.58931647109504</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.792967737035758</v>
       </c>
       <c r="E13">
-        <v>-15.33451445434011</v>
+        <v>-16.38768993530146</v>
       </c>
       <c r="F13">
-        <v>0.5327312131668823</v>
+        <v>0.1834840608399855</v>
       </c>
       <c r="G13">
-        <v>-8.101656849484483</v>
+        <v>-6.16940692180497</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.498702589080164</v>
       </c>
       <c r="E14">
-        <v>-15.46412787336536</v>
+        <v>-17.99841327056441</v>
       </c>
       <c r="F14">
-        <v>0.970436406969127</v>
+        <v>0.4020247774139539</v>
       </c>
       <c r="G14">
-        <v>-6.336865301368158</v>
+        <v>-6.064851822420064</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.258796788065685</v>
       </c>
       <c r="E15">
-        <v>-18.69095710576825</v>
+        <v>-19.63267700761649</v>
       </c>
       <c r="F15">
-        <v>0.7808496162252099</v>
+        <v>0.8379655486482357</v>
       </c>
       <c r="G15">
-        <v>-6.947774314199485</v>
+        <v>-5.849736911090694</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.087171437818493</v>
       </c>
       <c r="E16">
-        <v>-19.01450888081769</v>
+        <v>-19.58571664716666</v>
       </c>
       <c r="F16">
-        <v>1.006105907333674</v>
+        <v>1.080967126259471</v>
       </c>
       <c r="G16">
-        <v>-6.250238185090428</v>
+        <v>-5.330222234160471</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.99679626485964</v>
       </c>
       <c r="E17">
-        <v>-18.34023086902045</v>
+        <v>-20.28640077656716</v>
       </c>
       <c r="F17">
-        <v>1.336400841851921</v>
+        <v>1.191948477416937</v>
       </c>
       <c r="G17">
-        <v>-6.011496035211483</v>
+        <v>-5.20834745515812</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.987053580045594</v>
       </c>
       <c r="E18">
-        <v>-20.78753140823229</v>
+        <v>-21.46098293097589</v>
       </c>
       <c r="F18">
-        <v>1.375069032214602</v>
+        <v>1.944172348551112</v>
       </c>
       <c r="G18">
-        <v>-5.418152111989166</v>
+        <v>-5.098837162539282</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.055459856410145</v>
       </c>
       <c r="E19">
-        <v>-20.74267672592415</v>
+        <v>-22.38204475969444</v>
       </c>
       <c r="F19">
-        <v>2.194599411561042</v>
+        <v>2.049703042198158</v>
       </c>
       <c r="G19">
-        <v>-5.267016107609618</v>
+        <v>-4.725524182711403</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.187824579520472</v>
       </c>
       <c r="E20">
-        <v>-21.52407021100004</v>
+        <v>-22.8857877612829</v>
       </c>
       <c r="F20">
-        <v>1.80463220281473</v>
+        <v>2.442397236434486</v>
       </c>
       <c r="G20">
-        <v>-5.780719267080023</v>
+        <v>-4.632116962730551</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.365492346595366</v>
       </c>
       <c r="E21">
-        <v>-22.20947052272517</v>
+        <v>-23.80334843285462</v>
       </c>
       <c r="F21">
-        <v>2.264782011395827</v>
+        <v>3.080800112954398</v>
       </c>
       <c r="G21">
-        <v>-4.619522730823021</v>
+        <v>-4.393458356678521</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.567393432890583</v>
       </c>
       <c r="E22">
-        <v>-23.87642418611497</v>
+        <v>-24.40771543842101</v>
       </c>
       <c r="F22">
-        <v>2.805475639285926</v>
+        <v>2.955517826955001</v>
       </c>
       <c r="G22">
-        <v>-5.39407843611451</v>
+        <v>-4.698108753760122</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.766587618087196</v>
       </c>
       <c r="E23">
-        <v>-24.68853066893797</v>
+        <v>-24.76192621947034</v>
       </c>
       <c r="F23">
-        <v>3.13674307713506</v>
+        <v>3.136978333477455</v>
       </c>
       <c r="G23">
-        <v>-5.534536495116405</v>
+        <v>-3.993372191068775</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.94288954543403</v>
       </c>
       <c r="E24">
-        <v>-23.76394276380464</v>
+        <v>-25.42576721120829</v>
       </c>
       <c r="F24">
-        <v>3.137571444537859</v>
+        <v>3.108280373174869</v>
       </c>
       <c r="G24">
-        <v>-5.264569839927745</v>
+        <v>-4.463919742448078</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.075386569695623</v>
       </c>
       <c r="E25">
-        <v>-24.58426845183948</v>
+        <v>-25.26730558632078</v>
       </c>
       <c r="F25">
-        <v>3.108890051583329</v>
+        <v>3.011252042550157</v>
       </c>
       <c r="G25">
-        <v>-5.460623704997397</v>
+        <v>-4.605255011632587</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.153304517691301</v>
       </c>
       <c r="E26">
-        <v>-24.41544456469652</v>
+        <v>-25.81142195519789</v>
       </c>
       <c r="F26">
-        <v>3.002209583981198</v>
+        <v>3.188791057787758</v>
       </c>
       <c r="G26">
-        <v>-4.995919000013005</v>
+        <v>-5.014087171622563</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.169866274287776</v>
       </c>
       <c r="E27">
-        <v>-25.09052414627945</v>
+        <v>-26.13959625445187</v>
       </c>
       <c r="F27">
-        <v>2.902492372766999</v>
+        <v>3.389421642745798</v>
       </c>
       <c r="G27">
-        <v>-5.825976524566973</v>
+        <v>-4.877610498122116</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.123899946237421</v>
       </c>
       <c r="E28">
-        <v>-24.6321632848374</v>
+        <v>-26.22036375508581</v>
       </c>
       <c r="F28">
-        <v>3.13632889343366</v>
+        <v>2.884273260109826</v>
       </c>
       <c r="G28">
-        <v>-5.992920587445711</v>
+        <v>-4.717994795310632</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.018523715838693</v>
       </c>
       <c r="E29">
-        <v>-26.12093587596941</v>
+        <v>-26.13853303235271</v>
       </c>
       <c r="F29">
-        <v>3.572656512245049</v>
+        <v>2.63108939038338</v>
       </c>
       <c r="G29">
-        <v>-5.458185269549297</v>
+        <v>-5.037330630717245</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.854915613067104</v>
       </c>
       <c r="E30">
-        <v>-25.44739298257667</v>
+        <v>-25.94107690633639</v>
       </c>
       <c r="F30">
-        <v>3.149282902878639</v>
+        <v>2.703821705083982</v>
       </c>
       <c r="G30">
-        <v>-6.113260248628487</v>
+        <v>-4.772499310139304</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.640051002678727</v>
       </c>
       <c r="E31">
-        <v>-24.4237551405575</v>
+        <v>-25.55960029293956</v>
       </c>
       <c r="F31">
-        <v>2.690784858898724</v>
+        <v>2.601407329606268</v>
       </c>
       <c r="G31">
-        <v>-5.650171594545995</v>
+        <v>-4.551703418579671</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.378523878129193</v>
       </c>
       <c r="E32">
-        <v>-24.34529267220884</v>
+        <v>-24.97283875017911</v>
       </c>
       <c r="F32">
-        <v>2.68377687067104</v>
+        <v>2.575459549080976</v>
       </c>
       <c r="G32">
-        <v>-5.441228483430017</v>
+        <v>-4.426818451063767</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.082274537028157</v>
       </c>
       <c r="E33">
-        <v>-23.93145423616895</v>
+        <v>-25.16984632937235</v>
       </c>
       <c r="F33">
-        <v>2.896612620941928</v>
+        <v>2.381667965400449</v>
       </c>
       <c r="G33">
-        <v>-6.182118637219101</v>
+        <v>-4.752641986779296</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.762212029547942</v>
       </c>
       <c r="E34">
-        <v>-24.35402272241363</v>
+        <v>-25.32979065070282</v>
       </c>
       <c r="F34">
-        <v>2.627489305650813</v>
+        <v>2.530590200340938</v>
       </c>
       <c r="G34">
-        <v>-5.667668804795636</v>
+        <v>-4.502728460794977</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.431732584577246</v>
       </c>
       <c r="E35">
-        <v>-22.55346440391542</v>
+        <v>-24.81666554473158</v>
       </c>
       <c r="F35">
-        <v>2.753512152108313</v>
+        <v>2.246249775860397</v>
       </c>
       <c r="G35">
-        <v>-5.29680209264963</v>
+        <v>-4.397935783652281</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.10503860490901</v>
       </c>
       <c r="E36">
-        <v>-23.22712774043658</v>
+        <v>-24.17279734625474</v>
       </c>
       <c r="F36">
-        <v>2.662075301452498</v>
+        <v>2.504856138605569</v>
       </c>
       <c r="G36">
-        <v>-5.431774977265595</v>
+        <v>-4.440407376660512</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.792640041372586</v>
       </c>
       <c r="E37">
-        <v>-22.94403239690229</v>
+        <v>-24.09529011651079</v>
       </c>
       <c r="F37">
-        <v>2.645521207274953</v>
+        <v>2.308412122501277</v>
       </c>
       <c r="G37">
-        <v>-4.9678352204464</v>
+        <v>-3.796213981037082</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.508155374082866</v>
       </c>
       <c r="E38">
-        <v>-21.22564951767713</v>
+        <v>-23.17909169825361</v>
       </c>
       <c r="F38">
-        <v>2.344757570666508</v>
+        <v>2.175263659644896</v>
       </c>
       <c r="G38">
-        <v>-4.903785823392617</v>
+        <v>-3.590972905751302</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.256311349831905</v>
       </c>
       <c r="E39">
-        <v>-22.45600514696699</v>
+        <v>-22.6604012891071</v>
       </c>
       <c r="F39">
-        <v>2.416717846947702</v>
+        <v>2.133850259709337</v>
       </c>
       <c r="G39">
-        <v>-4.683632175002399</v>
+        <v>-3.804093208213062</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.044035696339491</v>
       </c>
       <c r="E40">
-        <v>-20.85227997278637</v>
+        <v>-22.79955048133415</v>
       </c>
       <c r="F40">
-        <v>2.223458075139771</v>
+        <v>2.102002846541308</v>
       </c>
       <c r="G40">
-        <v>-4.712674097833943</v>
+        <v>-3.366649898249075</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.871968093740142</v>
       </c>
       <c r="E41">
-        <v>-20.69482757825079</v>
+        <v>-22.46986025994662</v>
       </c>
       <c r="F41">
-        <v>2.720405620488028</v>
+        <v>2.300249390114091</v>
       </c>
       <c r="G41">
-        <v>-4.427849695177257</v>
+        <v>-3.358467824700526</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.738648579234202</v>
       </c>
       <c r="E42">
-        <v>-21.23940495358496</v>
+        <v>-21.62888065199341</v>
       </c>
       <c r="F42">
-        <v>2.181756403348039</v>
+        <v>2.313586105299163</v>
       </c>
       <c r="G42">
-        <v>-4.549079620265602</v>
+        <v>-2.977985740225449</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.640313661617831</v>
       </c>
       <c r="E43">
-        <v>-20.43324586937912</v>
+        <v>-21.21051521560945</v>
       </c>
       <c r="F43">
-        <v>2.404789356347389</v>
+        <v>2.135041452034563</v>
       </c>
       <c r="G43">
-        <v>-4.786025577865862</v>
+        <v>-3.030558304056697</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.568575768700693</v>
       </c>
       <c r="E44">
-        <v>-19.02285268236927</v>
+        <v>-20.88831323424058</v>
       </c>
       <c r="F44">
-        <v>2.700798164063764</v>
+        <v>1.958751614840384</v>
       </c>
       <c r="G44">
-        <v>-4.718968603043117</v>
+        <v>-2.704750432808715</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.51947711709813</v>
       </c>
       <c r="E45">
-        <v>-19.80251427832271</v>
+        <v>-20.37973589467003</v>
       </c>
       <c r="F45">
-        <v>2.43228452718111</v>
+        <v>2.074562347956171</v>
       </c>
       <c r="G45">
-        <v>-3.905416205794168</v>
+        <v>-2.585765748068727</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.485444286075766</v>
       </c>
       <c r="E46">
-        <v>-19.0554927701711</v>
+        <v>-20.18864248840334</v>
       </c>
       <c r="F46">
-        <v>2.299586696191851</v>
+        <v>1.718089346774655</v>
       </c>
       <c r="G46">
-        <v>-3.990813661369484</v>
+        <v>-2.749650018286681</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.464140569222358</v>
       </c>
       <c r="E47">
-        <v>-18.78053772083348</v>
+        <v>-19.12178632933801</v>
       </c>
       <c r="F47">
-        <v>2.241094017145373</v>
+        <v>2.193780984567076</v>
       </c>
       <c r="G47">
-        <v>-4.059408364756394</v>
+        <v>-2.741718576218879</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.454886616694507</v>
       </c>
       <c r="E48">
-        <v>-16.7233857002647</v>
+        <v>-19.12175725685874</v>
       </c>
       <c r="F48">
-        <v>1.95680660817861</v>
+        <v>1.824758217233147</v>
       </c>
       <c r="G48">
-        <v>-4.013461870697392</v>
+        <v>-2.304933173891853</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.456271077017829</v>
       </c>
       <c r="E49">
-        <v>-17.47893375126618</v>
+        <v>-18.08043088780713</v>
       </c>
       <c r="F49">
-        <v>2.397072285622909</v>
+        <v>2.203890380350841</v>
       </c>
       <c r="G49">
-        <v>-3.780424197750029</v>
+        <v>-2.57707196858032</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.469802491114775</v>
       </c>
       <c r="E50">
-        <v>-16.93997567085451</v>
+        <v>-17.67988272800669</v>
       </c>
       <c r="F50">
-        <v>1.838555504694175</v>
+        <v>1.57410418155485</v>
       </c>
       <c r="G50">
-        <v>-3.678863622411131</v>
+        <v>-2.489497152016015</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.494968293700952</v>
       </c>
       <c r="E51">
-        <v>-16.93600520082797</v>
+        <v>-17.58545116211406</v>
       </c>
       <c r="F51">
-        <v>2.420213557387515</v>
+        <v>1.76115285457659</v>
       </c>
       <c r="G51">
-        <v>-3.979866809298946</v>
+        <v>-1.769503397934203</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.532706705734201</v>
       </c>
       <c r="E52">
-        <v>-16.03207536882434</v>
+        <v>-17.28312645014582</v>
       </c>
       <c r="F52">
-        <v>1.952197571949434</v>
+        <v>1.881844328429672</v>
       </c>
       <c r="G52">
-        <v>-4.363111061551421</v>
+        <v>-2.539665220078848</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.578810586096993</v>
       </c>
       <c r="E53">
-        <v>-15.61565363534041</v>
+        <v>-16.55948336854167</v>
       </c>
       <c r="F53">
-        <v>1.782209953955753</v>
+        <v>1.599783571041635</v>
       </c>
       <c r="G53">
-        <v>-3.860814245199589</v>
+        <v>-2.182546688949644</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.627844673640629</v>
       </c>
       <c r="E54">
-        <v>-14.74407731955719</v>
+        <v>-16.79869588121782</v>
       </c>
       <c r="F54">
-        <v>2.045824626018251</v>
+        <v>1.72289056424128</v>
       </c>
       <c r="G54">
-        <v>-3.857224471386808</v>
+        <v>-2.38357924395455</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.673720664659366</v>
       </c>
       <c r="E55">
-        <v>-15.62108188254196</v>
+        <v>-16.14101410187459</v>
       </c>
       <c r="F55">
-        <v>2.066210747801147</v>
+        <v>1.703165479645819</v>
       </c>
       <c r="G55">
-        <v>-4.262767093191981</v>
+        <v>-2.422839621115711</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.70976660163455</v>
       </c>
       <c r="E56">
-        <v>-15.05175967413446</v>
+        <v>-15.34551631113958</v>
       </c>
       <c r="F56">
-        <v>1.573880522356094</v>
+        <v>1.631992152397285</v>
       </c>
       <c r="G56">
-        <v>-3.767626327764391</v>
+        <v>-2.538064833644496</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.733586181887822</v>
       </c>
       <c r="E57">
-        <v>-13.78913774606201</v>
+        <v>-15.24422779334966</v>
       </c>
       <c r="F57">
-        <v>1.895893439581152</v>
+        <v>1.655423352752872</v>
       </c>
       <c r="G57">
-        <v>-4.642653927900285</v>
+        <v>-2.71587742625604</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.740695455497853</v>
       </c>
       <c r="E58">
-        <v>-15.01411496668621</v>
+        <v>-15.29946550396988</v>
       </c>
       <c r="F58">
-        <v>1.748462265965701</v>
+        <v>1.613650441364498</v>
       </c>
       <c r="G58">
-        <v>-4.846344220898943</v>
+        <v>-2.798619754582193</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.730295679501603</v>
       </c>
       <c r="E59">
-        <v>-14.31513780714022</v>
+        <v>-14.7188216414909</v>
       </c>
       <c r="F59">
-        <v>1.858567204411006</v>
+        <v>1.560784033717834</v>
       </c>
       <c r="G59">
-        <v>-4.0411044344281</v>
+        <v>-3.184258059624719</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.699830844925873</v>
       </c>
       <c r="E60">
-        <v>-13.23207997069673</v>
+        <v>-14.99569962767193</v>
       </c>
       <c r="F60">
-        <v>1.554821445152483</v>
+        <v>1.829963677992339</v>
       </c>
       <c r="G60">
-        <v>-4.979541799192952</v>
+        <v>-2.941787766469663</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.649627153318054</v>
       </c>
       <c r="E61">
-        <v>-13.38701136595814</v>
+        <v>-14.01725287807822</v>
       </c>
       <c r="F61">
-        <v>1.365769779750774</v>
+        <v>1.701864942823423</v>
       </c>
       <c r="G61">
-        <v>-4.810347274476674</v>
+        <v>-3.305349615249735</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.580049082012032</v>
       </c>
       <c r="E62">
-        <v>-14.28397210935871</v>
+        <v>-14.54226862807244</v>
       </c>
       <c r="F62">
-        <v>1.573991523588069</v>
+        <v>1.564142235168783</v>
       </c>
       <c r="G62">
-        <v>-5.115049886450096</v>
+        <v>-3.737493113693762</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.490438309764988</v>
       </c>
       <c r="E63">
-        <v>-11.49083781633972</v>
+        <v>-13.51670784920988</v>
       </c>
       <c r="F63">
-        <v>1.357237595501939</v>
+        <v>1.754878799867786</v>
       </c>
       <c r="G63">
-        <v>-6.147698580529863</v>
+        <v>-4.357983559174474</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.382166234193463</v>
       </c>
       <c r="E64">
-        <v>-12.39371273266684</v>
+        <v>-13.50665292459247</v>
       </c>
       <c r="F64">
-        <v>2.00122366831672</v>
+        <v>1.67699072645216</v>
       </c>
       <c r="G64">
-        <v>-6.202474612796011</v>
+        <v>-4.481672805667649</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.254056518890308</v>
       </c>
       <c r="E65">
-        <v>-12.89546219281938</v>
+        <v>-13.49975859379326</v>
       </c>
       <c r="F65">
-        <v>1.579881215821974</v>
+        <v>1.560260505519265</v>
       </c>
       <c r="G65">
-        <v>-6.334340711348552</v>
+        <v>-4.204800731035493</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.109231187160084</v>
       </c>
       <c r="E66">
-        <v>-13.72307676672929</v>
+        <v>-13.19867153879981</v>
       </c>
       <c r="F66">
-        <v>1.306935813334342</v>
+        <v>1.575023669371957</v>
       </c>
       <c r="G66">
-        <v>-5.380416409669214</v>
+        <v>-4.532877339333153</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.948388816576584</v>
       </c>
       <c r="E67">
-        <v>-13.2152303923519</v>
+        <v>-12.67098942713505</v>
       </c>
       <c r="F67">
-        <v>1.53077890965363</v>
+        <v>1.462718587104817</v>
       </c>
       <c r="G67">
-        <v>-6.305403218300651</v>
+        <v>-4.834896105866911</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.776323897129263</v>
       </c>
       <c r="E68">
-        <v>-12.991197867068</v>
+        <v>-13.41700170493472</v>
       </c>
       <c r="F68">
-        <v>1.362769433017835</v>
+        <v>1.427869170469042</v>
       </c>
       <c r="G68">
-        <v>-6.626441259180671</v>
+        <v>-5.446925128127826</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.59595182468584</v>
       </c>
       <c r="E69">
-        <v>-12.29774032537271</v>
+        <v>-12.99371055991952</v>
       </c>
       <c r="F69">
-        <v>1.450357688720243</v>
+        <v>1.475041380588863</v>
       </c>
       <c r="G69">
-        <v>-6.175555225317042</v>
+        <v>-5.29539751205961</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.410092861703387</v>
       </c>
       <c r="E70">
-        <v>-11.6148194808085</v>
+        <v>-12.55956292050122</v>
       </c>
       <c r="F70">
-        <v>0.8204223837917478</v>
+        <v>1.321303017568497</v>
       </c>
       <c r="G70">
-        <v>-6.873558677707908</v>
+        <v>-4.754673146071182</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.222011857332133</v>
       </c>
       <c r="E71">
-        <v>-11.83770156655542</v>
+        <v>-13.07850252232722</v>
       </c>
       <c r="F71">
-        <v>1.777330869953264</v>
+        <v>1.293463245895211</v>
       </c>
       <c r="G71">
-        <v>-6.767212607533499</v>
+        <v>-5.129286276705437</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.031244415747262</v>
       </c>
       <c r="E72">
-        <v>-11.92655121642748</v>
+        <v>-12.47053052933087</v>
       </c>
       <c r="F72">
-        <v>1.346081143321036</v>
+        <v>1.625969921378933</v>
       </c>
       <c r="G72">
-        <v>-6.438462427131332</v>
+        <v>-4.892322043893039</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.840470347605107</v>
       </c>
       <c r="E73">
-        <v>-13.68765402733982</v>
+        <v>-12.28016808825735</v>
       </c>
       <c r="F73">
-        <v>0.8831049451615864</v>
+        <v>1.24147656443032</v>
       </c>
       <c r="G73">
-        <v>-6.190754980326503</v>
+        <v>-5.233629905778462</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.647973406100113</v>
       </c>
       <c r="E74">
-        <v>-12.01231503028519</v>
+        <v>-12.57699394843153</v>
       </c>
       <c r="F74">
-        <v>1.462675511999872</v>
+        <v>1.178214145878521</v>
       </c>
       <c r="G74">
-        <v>-6.779814671674803</v>
+        <v>-5.471505288453157</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.456006888837657</v>
       </c>
       <c r="E75">
-        <v>-12.06997406310778</v>
+        <v>-12.95408892388066</v>
       </c>
       <c r="F75">
-        <v>0.9501513460093728</v>
+        <v>1.094641815344885</v>
       </c>
       <c r="G75">
-        <v>-6.456382578004733</v>
+        <v>-5.335101715801262</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.264165573827094</v>
       </c>
       <c r="E76">
-        <v>-13.55440654840535</v>
+        <v>-13.03538388235285</v>
       </c>
       <c r="F76">
-        <v>1.01382463479296</v>
+        <v>1.450521705465997</v>
       </c>
       <c r="G76">
-        <v>-7.117710290379639</v>
+        <v>-5.3229278137729</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.07284343127998</v>
       </c>
       <c r="E77">
-        <v>-12.93288262685608</v>
+        <v>-13.78175748953779</v>
       </c>
       <c r="F77">
-        <v>0.430689603020428</v>
+        <v>1.077352130913654</v>
       </c>
       <c r="G77">
-        <v>-6.406976847362506</v>
+        <v>-5.128069669725978</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.8834671418653377</v>
       </c>
       <c r="E78">
-        <v>-12.82328353320518</v>
+        <v>-14.16422672044125</v>
       </c>
       <c r="F78">
-        <v>0.6367153448729015</v>
+        <v>0.9044950482366753</v>
       </c>
       <c r="G78">
-        <v>-6.166772680512536</v>
+        <v>-4.786474625935533</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.6948743626176046</v>
       </c>
       <c r="E79">
-        <v>-13.20028713800517</v>
+        <v>-13.96976921300145</v>
       </c>
       <c r="F79">
-        <v>0.7559770565887519</v>
+        <v>0.8585703594254707</v>
       </c>
       <c r="G79">
-        <v>-6.595135820788631</v>
+        <v>-4.860570168175919</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.5094778947610192</v>
       </c>
       <c r="E80">
-        <v>-14.10105637619061</v>
+        <v>-13.74729414196436</v>
       </c>
       <c r="F80">
-        <v>0.479277493031633</v>
+        <v>0.8143255997071435</v>
       </c>
       <c r="G80">
-        <v>-5.409669802812639</v>
+        <v>-5.044951394178704</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.3262781725138768</v>
       </c>
       <c r="E81">
-        <v>-13.95439402467694</v>
+        <v>-14.74159785239626</v>
       </c>
       <c r="F81">
-        <v>0.6875936707528471</v>
+        <v>0.772151758495815</v>
       </c>
       <c r="G81">
-        <v>-5.60832396949504</v>
+        <v>-4.207680382319491</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.1481978261478492</v>
       </c>
       <c r="E82">
-        <v>-15.14975884855511</v>
+        <v>-15.25449453174464</v>
       </c>
       <c r="F82">
-        <v>0.4345887283854053</v>
+        <v>0.4981104259342798</v>
       </c>
       <c r="G82">
-        <v>-5.376800528410523</v>
+        <v>-4.416926339808039</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.02367981032376569</v>
       </c>
       <c r="E83">
-        <v>-15.93793452772445</v>
+        <v>-16.16577554779322</v>
       </c>
       <c r="F83">
-        <v>-0.1147066666153637</v>
+        <v>0.479339620586843</v>
       </c>
       <c r="G83">
-        <v>-6.484461136082157</v>
+        <v>-4.294166518389301</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.1874195926312763</v>
       </c>
       <c r="E84">
-        <v>-17.42146576616453</v>
+        <v>-17.46656548794084</v>
       </c>
       <c r="F84">
-        <v>0.3151273801254802</v>
+        <v>0.5006029834493034</v>
       </c>
       <c r="G84">
-        <v>-4.584170638314756</v>
+        <v>-4.209468742364404</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.3404360595348661</v>
       </c>
       <c r="E85">
-        <v>-18.64090675609274</v>
+        <v>-18.66196353750962</v>
       </c>
       <c r="F85">
-        <v>0.1164393167270047</v>
+        <v>0.3820039656556927</v>
       </c>
       <c r="G85">
-        <v>-5.468014722934838</v>
+        <v>-3.959719693289325</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.4806533176446186</v>
       </c>
       <c r="E86">
-        <v>-19.04800453015243</v>
+        <v>-18.59976919792031</v>
       </c>
       <c r="F86">
-        <v>0.02469679849955671</v>
+        <v>0.3932399411072652</v>
       </c>
       <c r="G86">
-        <v>-5.303796277409222</v>
+        <v>-4.055789872753111</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.6031726611768617</v>
       </c>
       <c r="E87">
-        <v>-20.62065122398936</v>
+        <v>-20.02324084739205</v>
       </c>
       <c r="F87">
-        <v>-0.322922611880839</v>
+        <v>0.07509549965328143</v>
       </c>
       <c r="G87">
-        <v>-6.320796168409855</v>
+        <v>-4.089828760732046</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.7022156084412929</v>
       </c>
       <c r="E88">
-        <v>-20.71703895241598</v>
+        <v>-21.76141377858001</v>
       </c>
       <c r="F88">
-        <v>-0.3866870210787338</v>
+        <v>0.01020119731796816</v>
       </c>
       <c r="G88">
-        <v>-5.500743017129035</v>
+        <v>-4.009689344763233</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.770372184545824</v>
       </c>
       <c r="E89">
-        <v>-22.24417475655543</v>
+        <v>-22.38452422685537</v>
       </c>
       <c r="F89">
-        <v>-0.1884040293402273</v>
+        <v>0.03001077538851554</v>
       </c>
       <c r="G89">
-        <v>-5.529346334869272</v>
+        <v>-4.180001268164508</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.7989386231310664</v>
       </c>
       <c r="E90">
-        <v>-23.64663115672354</v>
+        <v>-24.16084025085056</v>
       </c>
       <c r="F90">
-        <v>-0.2117441092815062</v>
+        <v>-0.3388057284621168</v>
       </c>
       <c r="G90">
-        <v>-5.345283619706604</v>
+        <v>-3.855827723030563</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.779432664666688</v>
       </c>
       <c r="E91">
-        <v>-26.70283400826849</v>
+        <v>-26.38562003370074</v>
       </c>
       <c r="F91">
-        <v>-0.1921590187771175</v>
+        <v>-0.3043398459338377</v>
       </c>
       <c r="G91">
-        <v>-5.101813411373151</v>
+        <v>-4.211928063769233</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.7032624486838144</v>
       </c>
       <c r="E92">
-        <v>-28.1865292985559</v>
+        <v>-27.67277498106895</v>
       </c>
       <c r="F92">
-        <v>-0.4201472655800142</v>
+        <v>-0.237203981406549</v>
       </c>
       <c r="G92">
-        <v>-5.804745949552039</v>
+        <v>-4.227065160908507</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.5623330925403885</v>
       </c>
       <c r="E93">
-        <v>-29.77322422969906</v>
+        <v>-30.00228421729167</v>
       </c>
       <c r="F93">
-        <v>-0.5265444315303883</v>
+        <v>-0.330372119934215</v>
       </c>
       <c r="G93">
-        <v>-5.759812424394388</v>
+        <v>-4.219791626477666</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.3540364414095878</v>
       </c>
       <c r="E94">
-        <v>-32.87121046377745</v>
+        <v>-31.54441519091941</v>
       </c>
       <c r="F94">
-        <v>-0.7239650928025805</v>
+        <v>-0.5221242630690501</v>
       </c>
       <c r="G94">
-        <v>-5.850269502987282</v>
+        <v>-4.523288074449994</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.07704320810671533</v>
       </c>
       <c r="E95">
-        <v>-34.53775711245743</v>
+        <v>-34.09834527768491</v>
       </c>
       <c r="F95">
-        <v>-0.8793088318495718</v>
+        <v>-0.8615304106506888</v>
       </c>
       <c r="G95">
-        <v>-6.615014030105367</v>
+        <v>-4.496911721845977</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.2677046662700914</v>
       </c>
       <c r="E96">
-        <v>-36.93250914538188</v>
+        <v>-36.19797634368403</v>
       </c>
       <c r="F96">
-        <v>-0.7148812158634811</v>
+        <v>-0.8570911897390863</v>
       </c>
       <c r="G96">
-        <v>-6.208231304619416</v>
+        <v>-4.858251826979011</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.6685465015808414</v>
       </c>
       <c r="E97">
-        <v>-38.47130509031579</v>
+        <v>-38.51440919405052</v>
       </c>
       <c r="F97">
-        <v>-0.3973920130251118</v>
+        <v>-1.080344488467581</v>
       </c>
       <c r="G97">
-        <v>-5.624121585015867</v>
+        <v>-5.088156606417038</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.126357676805962</v>
       </c>
       <c r="E98">
-        <v>-40.52869176732441</v>
+        <v>-40.49035139697926</v>
       </c>
       <c r="F98">
-        <v>-0.2276553903544791</v>
+        <v>-0.9029297283403996</v>
       </c>
       <c r="G98">
-        <v>-6.574317743419094</v>
+        <v>-4.932211610500659</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.608500641131055</v>
       </c>
       <c r="E99">
-        <v>-43.03292452737701</v>
+        <v>-42.82198707740029</v>
       </c>
       <c r="F99">
-        <v>-0.9113716205423295</v>
+        <v>-0.8427239855049315</v>
       </c>
       <c r="G99">
-        <v>-6.367894000833539</v>
+        <v>-5.727517513802317</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.128094800129481</v>
       </c>
       <c r="E100">
-        <v>-46.27326415621956</v>
+        <v>-45.1053852848891</v>
       </c>
       <c r="F100">
-        <v>-1.001757272963992</v>
+        <v>-1.095508582143229</v>
       </c>
       <c r="G100">
-        <v>-6.462828506400192</v>
+        <v>-5.708923790824408</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.618606481077469</v>
       </c>
       <c r="E101">
-        <v>-48.06088106822961</v>
+        <v>-47.46808802432268</v>
       </c>
       <c r="F101">
-        <v>-0.7058718919906337</v>
+        <v>-1.173607889246569</v>
       </c>
       <c r="G101">
-        <v>-7.156490290536036</v>
+        <v>-6.308230654692828</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.138617740915019</v>
       </c>
       <c r="E102">
-        <v>-50.47912574101295</v>
+        <v>-50.0893738540514</v>
       </c>
       <c r="F102">
-        <v>-1.025744307846857</v>
+        <v>-1.218201391641475</v>
       </c>
       <c r="G102">
-        <v>-8.660040291887203</v>
+        <v>-5.832613037317582</v>
       </c>
     </row>
   </sheetData>
